--- a/data/trans_dic/KIDM_C_3_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor)</t>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 11,18</t>
+          <t>1,33; 10,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 21,66</t>
+          <t>6,16; 20,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 18,83</t>
+          <t>1,95; 17,9</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,1; 10,98</t>
+          <t>1,12; 10,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 23,26</t>
+          <t>4,24; 21,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,03; 30,66</t>
+          <t>9,2; 29,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 8,5</t>
+          <t>1,4; 8,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,9; 18,02</t>
+          <t>6,34; 17,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 20,01</t>
+          <t>7,05; 20,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 4,78</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 8,82</t>
+          <t>3,55; 8,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,68; 22,68</t>
+          <t>13,49; 22,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,29</t>
+          <t>6,22; 12,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 8,66</t>
+          <t>2,38; 8,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,86</t>
+          <t>2,29; 6,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,61; 15,87</t>
+          <t>8,75; 15,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,87; 13,45</t>
+          <t>6,46; 12,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,9</t>
+          <t>0,83; 4,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 6,75</t>
+          <t>3,32; 6,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,02; 17,74</t>
+          <t>12,1; 17,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,01; 11,39</t>
+          <t>7,2; 11,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,54</t>
+          <t>2,03; 5,61</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,14</t>
+          <t>1,32; 12,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 17,79</t>
+          <t>4,56; 18,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,66; 18,38</t>
+          <t>5,37; 17,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 10,74</t>
+          <t>0,77; 10,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 20,94</t>
+          <t>6,25; 21,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 15,05</t>
+          <t>4,19; 15,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,66</t>
+          <t>0,0; 6,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 9,22</t>
+          <t>2,04; 9,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 15,94</t>
+          <t>6,75; 16,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 14,5</t>
+          <t>6,13; 14,55</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,58; 7,76</t>
+          <t>3,53; 7,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,01; 18,83</t>
+          <t>11,93; 18,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,9; 12,01</t>
+          <t>6,5; 11,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,96</t>
+          <t>1,71; 6,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,11</t>
+          <t>2,6; 6,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,02; 14,99</t>
+          <t>8,87; 14,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 13,27</t>
+          <t>7,49; 12,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,15</t>
+          <t>0,79; 3,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 6,3</t>
+          <t>3,41; 6,25</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,31; 15,76</t>
+          <t>11,33; 15,8</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,83; 11,52</t>
+          <t>7,86; 11,51</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,17</t>
+          <t>1,76; 4,46</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1838</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6192</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2213</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>6255</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3568</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10915</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>8468</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>602; 4941</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3182; 10807</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>598; 5478</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>484; 4748</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1913; 9893</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3372; 10813</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1242; 7777</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>6136; 17370</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4742; 13795</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>10876</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35475</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21741</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7930</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9019</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>26577</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22390</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>19895</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>62051</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>44131</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12503</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>6764; 17009</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>26944; 44511</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>15170; 30225</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>3787; 13820</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4975; 14456</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19563; 34392</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>15320; 30554</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1680; 9872</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>13542; 27961</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>51226; 74432</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>34624; 55450</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>7313; 20232</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2841</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5821</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>7575</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6568</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6448</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>4808</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>12390</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14023</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>718; 6571</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2772; 11268</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3817; 12757</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>380; 5269</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3452; 11651</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3165; 11814</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3378</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2111; 9617</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>7836; 19417</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>8991; 21336</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3440</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>15555</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>47488</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>31528</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7930</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12716</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>37868</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35092</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5213</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>28271</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>85356</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>66621</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>13143</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>10234; 22365</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>37239; 58394</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22477; 40964</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3597; 13483</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>8051; 19316</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>28717; 48243</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>26171; 44589</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2144; 10486</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>20429; 37446</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>72079; 100496</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>54592; 79978</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>8490; 21475</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/KIDM_C_3_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/KIDM_C_3_R-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 10,89</t>
+          <t>1,32; 10,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,16; 20,93</t>
+          <t>5,3; 20,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,95; 17,9</t>
+          <t>2,06; 19,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,99</t>
+          <t>1,11; 9,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 21,9</t>
+          <t>4,23; 20,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,2; 29,51</t>
+          <t>7,93; 31,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,4; 8,78</t>
+          <t>1,39; 8,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6,34; 17,95</t>
+          <t>6,96; 18,08</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 20,51</t>
+          <t>7,0; 20,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 8,93</t>
+          <t>3,47; 8,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 22,28</t>
+          <t>13,51; 22,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,22; 12,39</t>
+          <t>6,09; 12,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,38; 8,67</t>
+          <t>2,26; 9,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,65</t>
+          <t>2,26; 6,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 15,39</t>
+          <t>8,73; 15,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,46; 12,89</t>
+          <t>6,43; 13,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,9</t>
+          <t>0,81; 4,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,86</t>
+          <t>3,28; 6,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,1; 17,59</t>
+          <t>12,04; 17,53</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 11,53</t>
+          <t>7,31; 11,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,61</t>
+          <t>2,02; 5,52</t>
         </is>
       </c>
     </row>
@@ -997,17 +997,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 12,11</t>
+          <t>1,26; 11,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 18,53</t>
+          <t>4,57; 17,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 17,94</t>
+          <t>5,25; 17,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 10,74</t>
+          <t>1,3; 9,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 21,11</t>
+          <t>5,97; 20,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 15,65</t>
+          <t>4,23; 15,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,41</t>
+          <t>0,0; 5,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 9,31</t>
+          <t>2,0; 9,32</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6,75; 16,74</t>
+          <t>6,68; 16,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,13; 14,55</t>
+          <t>5,93; 14,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,71</t>
+          <t>3,44; 7,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,93; 18,71</t>
+          <t>12,33; 18,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,5; 11,85</t>
+          <t>6,74; 11,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,41</t>
+          <t>1,84; 6,78</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 6,24</t>
+          <t>2,46; 6,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,87; 14,9</t>
+          <t>8,91; 15,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 12,77</t>
+          <t>7,6; 12,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,87</t>
+          <t>0,79; 3,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,41; 6,25</t>
+          <t>3,49; 6,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,8</t>
+          <t>11,43; 15,74</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,51</t>
+          <t>7,85; 11,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,76; 4,46</t>
+          <t>1,53; 4,32</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores de los que se han reido mucho o muchísimo otros menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
+          <t>Menores de los/as que se han reído mucho o muchísimo otros/as menores (autopercepción menor) (tasa de respuesta: 94,62%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,17 +1504,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>602; 4941</t>
+          <t>597; 4984</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3182; 10807</t>
+          <t>2737; 10347</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>598; 5478</t>
+          <t>630; 5945</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1524,17 +1524,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>484; 4748</t>
+          <t>481; 4288</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1913; 9893</t>
+          <t>1911; 9323</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3372; 10813</t>
+          <t>2907; 11592</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1544,17 +1544,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1242; 7777</t>
+          <t>1231; 7321</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6136; 17370</t>
+          <t>6740; 17503</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4742; 13795</t>
+          <t>4706; 13896</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6764; 17009</t>
+          <t>6610; 16436</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26944; 44511</t>
+          <t>26993; 45043</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15170; 30225</t>
+          <t>14867; 30399</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3787; 13820</t>
+          <t>3593; 14751</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4975; 14456</t>
+          <t>4906; 14331</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19563; 34392</t>
+          <t>19511; 34483</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15320; 30554</t>
+          <t>15245; 31180</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1680; 9872</t>
+          <t>1634; 9678</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>13542; 27961</t>
+          <t>13368; 27668</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51226; 74432</t>
+          <t>50979; 74178</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34624; 55450</t>
+          <t>35183; 57412</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7313; 20232</t>
+          <t>7297; 19929</t>
         </is>
       </c>
     </row>
@@ -1920,17 +1920,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>718; 6571</t>
+          <t>684; 6365</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2772; 11268</t>
+          <t>2776; 10630</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3817; 12757</t>
+          <t>3732; 12581</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1940,42 +1940,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>380; 5269</t>
+          <t>637; 4702</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3452; 11651</t>
+          <t>3295; 11180</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3165; 11814</t>
+          <t>3196; 11347</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3378</t>
+          <t>0; 3016</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2111; 9617</t>
+          <t>2067; 9623</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7836; 19417</t>
+          <t>7750; 18938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8991; 21336</t>
+          <t>8694; 20995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 3440</t>
+          <t>0; 2972</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10234; 22365</t>
+          <t>9969; 22453</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37239; 58394</t>
+          <t>38490; 59050</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22477; 40964</t>
+          <t>23288; 41274</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3597; 13483</t>
+          <t>3869; 14270</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8051; 19316</t>
+          <t>7628; 18685</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28717; 48243</t>
+          <t>28856; 48894</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26171; 44589</t>
+          <t>26540; 45214</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2144; 10486</t>
+          <t>2142; 10620</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20429; 37446</t>
+          <t>20944; 37144</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72079; 100496</t>
+          <t>72671; 100119</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54592; 79978</t>
+          <t>54564; 79629</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8490; 21475</t>
+          <t>7381; 20811</t>
         </is>
       </c>
     </row>
